--- a/public/downloads/Programa_anual_auditoria.xlsx
+++ b/public/downloads/Programa_anual_auditoria.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\COMPUTADOR CASA\TODOS LOS DOCUMENTOS\PERSONAL VILMA LUCIA PERILLA\EMPRESAS\SENA DISEÑO INSTRUCCIONAL\Diseño I_Técnico CCC\Diseño Instruccional\CF10\MATERIAL COMPLEMENTARIO COM FORM 10\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angelicavaronquintero/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F2AE8A2-89E4-4BE9-A0DB-EE3462914F5A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{6B6D7660-8A9D-C04D-BD35-25F9DEE63983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFD65FA1-B49A-4D9D-84BE-85A039BDB5A9}"/>
   <bookViews>
-    <workbookView xWindow="-20520" yWindow="-105" windowWidth="20640" windowHeight="11160" xr2:uid="{352D5D0E-3784-4E75-A0D5-67C302F166BB}"/>
+    <workbookView xWindow="-34200" yWindow="780" windowWidth="34200" windowHeight="21460" firstSheet="1" xr2:uid="{352D5D0E-3784-4E75-A0D5-67C302F166BB}"/>
   </bookViews>
   <sheets>
-    <sheet name="EJEMPLO PROGRAMA DE AUDITORIAS" sheetId="1" r:id="rId1"/>
+    <sheet name="EJEMPLO PROGRAMA DE AUDITORÍAS" sheetId="1" r:id="rId1"/>
     <sheet name="PLANTILLA PROGRAMA DE AUDITOR" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,6 +28,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +39,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="50">
   <si>
-    <t>PROGRAMA ANUAL DE AUDITORIAS</t>
+    <t>PROGRAMA ANUAL DE AUDITORÍAS</t>
   </si>
   <si>
     <t>AÑO DEL PROGRAMA:</t>
@@ -52,12 +54,12 @@
     <t>OBJETIVOS:</t>
   </si>
   <si>
-    <t>Evaluar efecitvidad del sistema de gestión de calidad, atraves de auditorias internas y externas.
-Realizar analisis de resultados utilizando estadistica
-Establecer acciones de mejora alineados a conseguir objetivos estrategicos de la empresa.</t>
-  </si>
-  <si>
-    <t>CRONOGRAMA DE AUDITORIAS</t>
+    <t>Evaluar efectividad del sistema de gestión de calidad, a través de auditorías internas y externas.
+Realizar análisis de resultados utilizando estadística.
+Establecer acciones de mejora alineados a conseguir objetivos estratégicos de la empresa.</t>
+  </si>
+  <si>
+    <t>CRONOGRAMA DE AUDITORÍAS</t>
   </si>
   <si>
     <t>N°</t>
@@ -69,13 +71,13 @@
     <t>NORMAS, REGLAS</t>
   </si>
   <si>
-    <t>PROCESO/AREA</t>
-  </si>
-  <si>
-    <t>RESPONSABLE AUDITORIA</t>
-  </si>
-  <si>
-    <t>LIDER DE PROCESO</t>
+    <t>PROCESO/ÁREA</t>
+  </si>
+  <si>
+    <t>RESPONSABLE AUDITORÍA</t>
+  </si>
+  <si>
+    <t>LÍDER DE PROCESO</t>
   </si>
   <si>
     <t>MES/SEMANA</t>
@@ -117,16 +119,16 @@
     <t>DICIEMBRE</t>
   </si>
   <si>
-    <t>AUDITORIA DE GESTION</t>
-  </si>
-  <si>
-    <t>PRODUCCION/PATRONAJE</t>
+    <t>AUDITORÍA DE GESTIÓN</t>
+  </si>
+  <si>
+    <t>PRODUCCIÓN/PATRONAJE</t>
   </si>
   <si>
     <t>AUDITOR INTERNO 1</t>
   </si>
   <si>
-    <t>MARIA JACOME</t>
+    <t>MARÍA JÁCOME</t>
   </si>
   <si>
     <t>I</t>
@@ -138,10 +140,10 @@
     <t>PRODUCCIÓN/TRAZO Y CORTE</t>
   </si>
   <si>
-    <t>PAULA DIAZ</t>
-  </si>
-  <si>
-    <t>PRODUCCIÓN/CONFECCION</t>
+    <t>PAULA DÍAZ</t>
+  </si>
+  <si>
+    <t>PRODUCCIÓN/CONFECCIÓN</t>
   </si>
   <si>
     <t>AUDITOR INTERNO 2</t>
@@ -156,25 +158,25 @@
     <t>CARLOS CASTRO</t>
   </si>
   <si>
-    <t>GESTION DE CALIDAD</t>
+    <t>GESTIÓN DE CALIDAD</t>
   </si>
   <si>
     <t>AUDITOR INTERNO 3</t>
   </si>
   <si>
-    <t>EDUARDO JIMENEZ</t>
-  </si>
-  <si>
-    <t>DIRECCION</t>
+    <t>EDUARDO JIMÉNEZ</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN</t>
   </si>
   <si>
     <t>DIANA RIVERA</t>
   </si>
   <si>
-    <t>NÚMERO DE AUDITORIAS</t>
-  </si>
-  <si>
-    <t>TOTAL AUDITORIAS DEL PROGRAMA</t>
+    <t>NÚMERO DE AUDITORÍAS</t>
+  </si>
+  <si>
+    <t>TOTAL AUDITORÍAS DEL PROGRAMA</t>
   </si>
   <si>
     <t>ELABORADO POR</t>
@@ -186,14 +188,14 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>NOTA: EN CADA CASILLA ESPECIFICAR CON LETRA (I) SI ES INETERNA Y CON (E) SI ES EXTERNA</t>
+    <t>NOTA: EN CADA CASILLA ESPECIFICAR CON LETRA (I) SI ES INTERNA Y CON (E) SI ES EXTERNA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -584,16 +586,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
@@ -602,10 +595,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -617,16 +613,22 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -635,20 +637,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -688,6 +678,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -800,7 +802,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1097,314 +1099,314 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD5D58EE-5E08-4B45-A173-0B6015C0DA14}">
   <dimension ref="A1:BB24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="14.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="27.28515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" style="1" customWidth="1"/>
     <col min="6" max="6" width="27.85546875" customWidth="1"/>
     <col min="7" max="54" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
+    <row r="1" spans="1:54" ht="35.25" customHeight="1">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="47"/>
-      <c r="S1" s="47"/>
-      <c r="T1" s="47"/>
-      <c r="U1" s="47"/>
-      <c r="V1" s="47"/>
-      <c r="W1" s="47"/>
-      <c r="X1" s="47"/>
-      <c r="Y1" s="47"/>
-      <c r="Z1" s="47"/>
-      <c r="AA1" s="47"/>
-      <c r="AB1" s="47"/>
-      <c r="AC1" s="47"/>
-      <c r="AD1" s="47"/>
-      <c r="AE1" s="47"/>
-      <c r="AF1" s="47"/>
-      <c r="AG1" s="47"/>
-      <c r="AH1" s="47"/>
-      <c r="AI1" s="47"/>
-      <c r="AJ1" s="47"/>
-      <c r="AK1" s="47"/>
-      <c r="AL1" s="47"/>
-      <c r="AM1" s="47"/>
-      <c r="AN1" s="47"/>
-      <c r="AO1" s="47"/>
-      <c r="AP1" s="47"/>
-      <c r="AQ1" s="47"/>
-      <c r="AR1" s="47"/>
-      <c r="AS1" s="47"/>
-      <c r="AT1" s="47"/>
-      <c r="AU1" s="47"/>
-      <c r="AV1" s="47"/>
-      <c r="AW1" s="47"/>
-      <c r="AX1" s="47"/>
-      <c r="AY1" s="47"/>
-      <c r="AZ1" s="47"/>
-      <c r="BA1" s="47"/>
-      <c r="BB1" s="48"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="43"/>
+      <c r="W1" s="43"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="43"/>
+      <c r="AA1" s="43"/>
+      <c r="AB1" s="43"/>
+      <c r="AC1" s="43"/>
+      <c r="AD1" s="43"/>
+      <c r="AE1" s="43"/>
+      <c r="AF1" s="43"/>
+      <c r="AG1" s="43"/>
+      <c r="AH1" s="43"/>
+      <c r="AI1" s="43"/>
+      <c r="AJ1" s="43"/>
+      <c r="AK1" s="43"/>
+      <c r="AL1" s="43"/>
+      <c r="AM1" s="43"/>
+      <c r="AN1" s="43"/>
+      <c r="AO1" s="43"/>
+      <c r="AP1" s="43"/>
+      <c r="AQ1" s="43"/>
+      <c r="AR1" s="43"/>
+      <c r="AS1" s="43"/>
+      <c r="AT1" s="43"/>
+      <c r="AU1" s="43"/>
+      <c r="AV1" s="43"/>
+      <c r="AW1" s="43"/>
+      <c r="AX1" s="43"/>
+      <c r="AY1" s="43"/>
+      <c r="AZ1" s="43"/>
+      <c r="BA1" s="43"/>
+      <c r="BB1" s="44"/>
     </row>
-    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A2" s="49" t="s">
+    <row r="2" spans="1:54">
+      <c r="A2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="25">
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="27">
         <v>2020</v>
       </c>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="25"/>
-      <c r="Z2" s="25"/>
-      <c r="AA2" s="25"/>
-      <c r="AB2" s="25"/>
-      <c r="AC2" s="25"/>
-      <c r="AD2" s="25"/>
-      <c r="AE2" s="25"/>
-      <c r="AF2" s="25"/>
-      <c r="AG2" s="25"/>
-      <c r="AH2" s="25"/>
-      <c r="AI2" s="25"/>
-      <c r="AJ2" s="25"/>
-      <c r="AK2" s="25"/>
-      <c r="AL2" s="25"/>
-      <c r="AM2" s="25"/>
-      <c r="AN2" s="25"/>
-      <c r="AO2" s="25"/>
-      <c r="AP2" s="25"/>
-      <c r="AQ2" s="25"/>
-      <c r="AR2" s="25"/>
-      <c r="AS2" s="25"/>
-      <c r="AT2" s="25"/>
-      <c r="AU2" s="25"/>
-      <c r="AV2" s="25"/>
-      <c r="AW2" s="25"/>
-      <c r="AX2" s="25"/>
-      <c r="AY2" s="25"/>
-      <c r="AZ2" s="25"/>
-      <c r="BA2" s="25"/>
-      <c r="BB2" s="26"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+      <c r="V2" s="27"/>
+      <c r="W2" s="27"/>
+      <c r="X2" s="27"/>
+      <c r="Y2" s="27"/>
+      <c r="Z2" s="27"/>
+      <c r="AA2" s="27"/>
+      <c r="AB2" s="27"/>
+      <c r="AC2" s="27"/>
+      <c r="AD2" s="27"/>
+      <c r="AE2" s="27"/>
+      <c r="AF2" s="27"/>
+      <c r="AG2" s="27"/>
+      <c r="AH2" s="27"/>
+      <c r="AI2" s="27"/>
+      <c r="AJ2" s="27"/>
+      <c r="AK2" s="27"/>
+      <c r="AL2" s="27"/>
+      <c r="AM2" s="27"/>
+      <c r="AN2" s="27"/>
+      <c r="AO2" s="27"/>
+      <c r="AP2" s="27"/>
+      <c r="AQ2" s="27"/>
+      <c r="AR2" s="27"/>
+      <c r="AS2" s="27"/>
+      <c r="AT2" s="27"/>
+      <c r="AU2" s="27"/>
+      <c r="AV2" s="27"/>
+      <c r="AW2" s="27"/>
+      <c r="AX2" s="27"/>
+      <c r="AY2" s="27"/>
+      <c r="AZ2" s="27"/>
+      <c r="BA2" s="27"/>
+      <c r="BB2" s="28"/>
     </row>
-    <row r="3" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
+    <row r="3" spans="1:54">
+      <c r="A3" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="25" t="s">
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="25"/>
-      <c r="X3" s="25"/>
-      <c r="Y3" s="25"/>
-      <c r="Z3" s="25"/>
-      <c r="AA3" s="25"/>
-      <c r="AB3" s="25"/>
-      <c r="AC3" s="25"/>
-      <c r="AD3" s="25"/>
-      <c r="AE3" s="25"/>
-      <c r="AF3" s="25"/>
-      <c r="AG3" s="25"/>
-      <c r="AH3" s="25"/>
-      <c r="AI3" s="25"/>
-      <c r="AJ3" s="25"/>
-      <c r="AK3" s="25"/>
-      <c r="AL3" s="25"/>
-      <c r="AM3" s="25"/>
-      <c r="AN3" s="25"/>
-      <c r="AO3" s="25"/>
-      <c r="AP3" s="25"/>
-      <c r="AQ3" s="25"/>
-      <c r="AR3" s="25"/>
-      <c r="AS3" s="25"/>
-      <c r="AT3" s="25"/>
-      <c r="AU3" s="25"/>
-      <c r="AV3" s="25"/>
-      <c r="AW3" s="25"/>
-      <c r="AX3" s="25"/>
-      <c r="AY3" s="25"/>
-      <c r="AZ3" s="25"/>
-      <c r="BA3" s="25"/>
-      <c r="BB3" s="26"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="27"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="27"/>
+      <c r="V3" s="27"/>
+      <c r="W3" s="27"/>
+      <c r="X3" s="27"/>
+      <c r="Y3" s="27"/>
+      <c r="Z3" s="27"/>
+      <c r="AA3" s="27"/>
+      <c r="AB3" s="27"/>
+      <c r="AC3" s="27"/>
+      <c r="AD3" s="27"/>
+      <c r="AE3" s="27"/>
+      <c r="AF3" s="27"/>
+      <c r="AG3" s="27"/>
+      <c r="AH3" s="27"/>
+      <c r="AI3" s="27"/>
+      <c r="AJ3" s="27"/>
+      <c r="AK3" s="27"/>
+      <c r="AL3" s="27"/>
+      <c r="AM3" s="27"/>
+      <c r="AN3" s="27"/>
+      <c r="AO3" s="27"/>
+      <c r="AP3" s="27"/>
+      <c r="AQ3" s="27"/>
+      <c r="AR3" s="27"/>
+      <c r="AS3" s="27"/>
+      <c r="AT3" s="27"/>
+      <c r="AU3" s="27"/>
+      <c r="AV3" s="27"/>
+      <c r="AW3" s="27"/>
+      <c r="AX3" s="27"/>
+      <c r="AY3" s="27"/>
+      <c r="AZ3" s="27"/>
+      <c r="BA3" s="27"/>
+      <c r="BB3" s="28"/>
     </row>
-    <row r="4" spans="1:54" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
+    <row r="4" spans="1:54" ht="52.5" customHeight="1">
+      <c r="A4" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="55" t="s">
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="56"/>
-      <c r="Q4" s="56"/>
-      <c r="R4" s="56"/>
-      <c r="S4" s="56"/>
-      <c r="T4" s="56"/>
-      <c r="U4" s="56"/>
-      <c r="V4" s="56"/>
-      <c r="W4" s="56"/>
-      <c r="X4" s="56"/>
-      <c r="Y4" s="56"/>
-      <c r="Z4" s="56"/>
-      <c r="AA4" s="56"/>
-      <c r="AB4" s="56"/>
-      <c r="AC4" s="56"/>
-      <c r="AD4" s="56"/>
-      <c r="AE4" s="56"/>
-      <c r="AF4" s="56"/>
-      <c r="AG4" s="56"/>
-      <c r="AH4" s="56"/>
-      <c r="AI4" s="56"/>
-      <c r="AJ4" s="56"/>
-      <c r="AK4" s="56"/>
-      <c r="AL4" s="56"/>
-      <c r="AM4" s="56"/>
-      <c r="AN4" s="56"/>
-      <c r="AO4" s="56"/>
-      <c r="AP4" s="56"/>
-      <c r="AQ4" s="56"/>
-      <c r="AR4" s="56"/>
-      <c r="AS4" s="56"/>
-      <c r="AT4" s="56"/>
-      <c r="AU4" s="56"/>
-      <c r="AV4" s="56"/>
-      <c r="AW4" s="56"/>
-      <c r="AX4" s="56"/>
-      <c r="AY4" s="56"/>
-      <c r="AZ4" s="56"/>
-      <c r="BA4" s="56"/>
-      <c r="BB4" s="57"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="52"/>
+      <c r="N4" s="52"/>
+      <c r="O4" s="52"/>
+      <c r="P4" s="52"/>
+      <c r="Q4" s="52"/>
+      <c r="R4" s="52"/>
+      <c r="S4" s="52"/>
+      <c r="T4" s="52"/>
+      <c r="U4" s="52"/>
+      <c r="V4" s="52"/>
+      <c r="W4" s="52"/>
+      <c r="X4" s="52"/>
+      <c r="Y4" s="52"/>
+      <c r="Z4" s="52"/>
+      <c r="AA4" s="52"/>
+      <c r="AB4" s="52"/>
+      <c r="AC4" s="52"/>
+      <c r="AD4" s="52"/>
+      <c r="AE4" s="52"/>
+      <c r="AF4" s="52"/>
+      <c r="AG4" s="52"/>
+      <c r="AH4" s="52"/>
+      <c r="AI4" s="52"/>
+      <c r="AJ4" s="52"/>
+      <c r="AK4" s="52"/>
+      <c r="AL4" s="52"/>
+      <c r="AM4" s="52"/>
+      <c r="AN4" s="52"/>
+      <c r="AO4" s="52"/>
+      <c r="AP4" s="52"/>
+      <c r="AQ4" s="52"/>
+      <c r="AR4" s="52"/>
+      <c r="AS4" s="52"/>
+      <c r="AT4" s="52"/>
+      <c r="AU4" s="52"/>
+      <c r="AV4" s="52"/>
+      <c r="AW4" s="52"/>
+      <c r="AX4" s="52"/>
+      <c r="AY4" s="52"/>
+      <c r="AZ4" s="52"/>
+      <c r="BA4" s="52"/>
+      <c r="BB4" s="53"/>
     </row>
-    <row r="5" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
+    <row r="5" spans="1:54">
+      <c r="A5" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
-      <c r="S5" s="36"/>
-      <c r="T5" s="36"/>
-      <c r="U5" s="36"/>
-      <c r="V5" s="36"/>
-      <c r="W5" s="36"/>
-      <c r="X5" s="36"/>
-      <c r="Y5" s="36"/>
-      <c r="Z5" s="36"/>
-      <c r="AA5" s="36"/>
-      <c r="AB5" s="36"/>
-      <c r="AC5" s="36"/>
-      <c r="AD5" s="36"/>
-      <c r="AE5" s="36"/>
-      <c r="AF5" s="36"/>
-      <c r="AG5" s="36"/>
-      <c r="AH5" s="36"/>
-      <c r="AI5" s="36"/>
-      <c r="AJ5" s="36"/>
-      <c r="AK5" s="36"/>
-      <c r="AL5" s="36"/>
-      <c r="AM5" s="36"/>
-      <c r="AN5" s="36"/>
-      <c r="AO5" s="36"/>
-      <c r="AP5" s="36"/>
-      <c r="AQ5" s="36"/>
-      <c r="AR5" s="36"/>
-      <c r="AS5" s="36"/>
-      <c r="AT5" s="36"/>
-      <c r="AU5" s="36"/>
-      <c r="AV5" s="36"/>
-      <c r="AW5" s="36"/>
-      <c r="AX5" s="36"/>
-      <c r="AY5" s="36"/>
-      <c r="AZ5" s="36"/>
-      <c r="BA5" s="36"/>
-      <c r="BB5" s="37"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="56"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="56"/>
+      <c r="P5" s="56"/>
+      <c r="Q5" s="56"/>
+      <c r="R5" s="56"/>
+      <c r="S5" s="56"/>
+      <c r="T5" s="56"/>
+      <c r="U5" s="56"/>
+      <c r="V5" s="56"/>
+      <c r="W5" s="56"/>
+      <c r="X5" s="56"/>
+      <c r="Y5" s="56"/>
+      <c r="Z5" s="56"/>
+      <c r="AA5" s="56"/>
+      <c r="AB5" s="56"/>
+      <c r="AC5" s="56"/>
+      <c r="AD5" s="56"/>
+      <c r="AE5" s="56"/>
+      <c r="AF5" s="56"/>
+      <c r="AG5" s="56"/>
+      <c r="AH5" s="56"/>
+      <c r="AI5" s="56"/>
+      <c r="AJ5" s="56"/>
+      <c r="AK5" s="56"/>
+      <c r="AL5" s="56"/>
+      <c r="AM5" s="56"/>
+      <c r="AN5" s="56"/>
+      <c r="AO5" s="56"/>
+      <c r="AP5" s="56"/>
+      <c r="AQ5" s="56"/>
+      <c r="AR5" s="56"/>
+      <c r="AS5" s="56"/>
+      <c r="AT5" s="56"/>
+      <c r="AU5" s="56"/>
+      <c r="AV5" s="56"/>
+      <c r="AW5" s="56"/>
+      <c r="AX5" s="56"/>
+      <c r="AY5" s="56"/>
+      <c r="AZ5" s="56"/>
+      <c r="BA5" s="56"/>
+      <c r="BB5" s="57"/>
     </row>
-    <row r="6" spans="1:54" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:54" s="1" customFormat="1" ht="15.95" thickBot="1">
       <c r="A6" s="38" t="s">
         <v>7</v>
       </c>
@@ -1414,153 +1416,153 @@
       <c r="C6" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="34" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="40" t="s">
+      <c r="F6" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="43" t="s">
+      <c r="G6" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="43"/>
-      <c r="L6" s="43"/>
-      <c r="M6" s="43"/>
-      <c r="N6" s="43"/>
-      <c r="O6" s="43"/>
-      <c r="P6" s="43"/>
-      <c r="Q6" s="43"/>
-      <c r="R6" s="43"/>
-      <c r="S6" s="43"/>
-      <c r="T6" s="43"/>
-      <c r="U6" s="43"/>
-      <c r="V6" s="43"/>
-      <c r="W6" s="43"/>
-      <c r="X6" s="43"/>
-      <c r="Y6" s="43"/>
-      <c r="Z6" s="43"/>
-      <c r="AA6" s="43"/>
-      <c r="AB6" s="43"/>
-      <c r="AC6" s="43"/>
-      <c r="AD6" s="43"/>
-      <c r="AE6" s="43"/>
-      <c r="AF6" s="43"/>
-      <c r="AG6" s="43"/>
-      <c r="AH6" s="43"/>
-      <c r="AI6" s="43"/>
-      <c r="AJ6" s="43"/>
-      <c r="AK6" s="43"/>
-      <c r="AL6" s="43"/>
-      <c r="AM6" s="43"/>
-      <c r="AN6" s="43"/>
-      <c r="AO6" s="43"/>
-      <c r="AP6" s="43"/>
-      <c r="AQ6" s="43"/>
-      <c r="AR6" s="43"/>
-      <c r="AS6" s="43"/>
-      <c r="AT6" s="43"/>
-      <c r="AU6" s="43"/>
-      <c r="AV6" s="43"/>
-      <c r="AW6" s="43"/>
-      <c r="AX6" s="43"/>
-      <c r="AY6" s="43"/>
-      <c r="AZ6" s="43"/>
-      <c r="BA6" s="43"/>
-      <c r="BB6" s="44"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36"/>
+      <c r="T6" s="36"/>
+      <c r="U6" s="36"/>
+      <c r="V6" s="36"/>
+      <c r="W6" s="36"/>
+      <c r="X6" s="36"/>
+      <c r="Y6" s="36"/>
+      <c r="Z6" s="36"/>
+      <c r="AA6" s="36"/>
+      <c r="AB6" s="36"/>
+      <c r="AC6" s="36"/>
+      <c r="AD6" s="36"/>
+      <c r="AE6" s="36"/>
+      <c r="AF6" s="36"/>
+      <c r="AG6" s="36"/>
+      <c r="AH6" s="36"/>
+      <c r="AI6" s="36"/>
+      <c r="AJ6" s="36"/>
+      <c r="AK6" s="36"/>
+      <c r="AL6" s="36"/>
+      <c r="AM6" s="36"/>
+      <c r="AN6" s="36"/>
+      <c r="AO6" s="36"/>
+      <c r="AP6" s="36"/>
+      <c r="AQ6" s="36"/>
+      <c r="AR6" s="36"/>
+      <c r="AS6" s="36"/>
+      <c r="AT6" s="36"/>
+      <c r="AU6" s="36"/>
+      <c r="AV6" s="36"/>
+      <c r="AW6" s="36"/>
+      <c r="AX6" s="36"/>
+      <c r="AY6" s="36"/>
+      <c r="AZ6" s="36"/>
+      <c r="BA6" s="36"/>
+      <c r="BB6" s="37"/>
     </row>
-    <row r="7" spans="1:54" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:54" s="1" customFormat="1">
       <c r="A7" s="38"/>
       <c r="B7" s="39"/>
       <c r="C7" s="39"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="31" t="s">
+      <c r="D7" s="35"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="31" t="s">
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="L7" s="32"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="33"/>
-      <c r="O7" s="31" t="s">
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="P7" s="32"/>
-      <c r="Q7" s="32"/>
-      <c r="R7" s="33"/>
-      <c r="S7" s="31" t="s">
+      <c r="P7" s="30"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="31"/>
+      <c r="S7" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="T7" s="32"/>
-      <c r="U7" s="32"/>
-      <c r="V7" s="33"/>
-      <c r="W7" s="31" t="s">
+      <c r="T7" s="30"/>
+      <c r="U7" s="30"/>
+      <c r="V7" s="31"/>
+      <c r="W7" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="X7" s="32"/>
-      <c r="Y7" s="32"/>
-      <c r="Z7" s="33"/>
-      <c r="AA7" s="31" t="s">
+      <c r="X7" s="30"/>
+      <c r="Y7" s="30"/>
+      <c r="Z7" s="31"/>
+      <c r="AA7" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="AB7" s="32"/>
-      <c r="AC7" s="32"/>
-      <c r="AD7" s="33"/>
-      <c r="AE7" s="31" t="s">
+      <c r="AB7" s="30"/>
+      <c r="AC7" s="30"/>
+      <c r="AD7" s="31"/>
+      <c r="AE7" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="AF7" s="32"/>
-      <c r="AG7" s="32"/>
-      <c r="AH7" s="33"/>
-      <c r="AI7" s="31" t="s">
+      <c r="AF7" s="30"/>
+      <c r="AG7" s="30"/>
+      <c r="AH7" s="31"/>
+      <c r="AI7" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="AJ7" s="32"/>
-      <c r="AK7" s="32"/>
-      <c r="AL7" s="33"/>
-      <c r="AM7" s="31" t="s">
+      <c r="AJ7" s="30"/>
+      <c r="AK7" s="30"/>
+      <c r="AL7" s="31"/>
+      <c r="AM7" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="AN7" s="32"/>
-      <c r="AO7" s="32"/>
-      <c r="AP7" s="33"/>
-      <c r="AQ7" s="31" t="s">
+      <c r="AN7" s="30"/>
+      <c r="AO7" s="30"/>
+      <c r="AP7" s="31"/>
+      <c r="AQ7" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="AR7" s="32"/>
-      <c r="AS7" s="32"/>
-      <c r="AT7" s="33"/>
-      <c r="AU7" s="31" t="s">
+      <c r="AR7" s="30"/>
+      <c r="AS7" s="30"/>
+      <c r="AT7" s="31"/>
+      <c r="AU7" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="AV7" s="32"/>
-      <c r="AW7" s="32"/>
-      <c r="AX7" s="33"/>
-      <c r="AY7" s="31" t="s">
+      <c r="AV7" s="30"/>
+      <c r="AW7" s="30"/>
+      <c r="AX7" s="31"/>
+      <c r="AY7" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="AZ7" s="32"/>
-      <c r="BA7" s="32"/>
-      <c r="BB7" s="33"/>
+      <c r="AZ7" s="30"/>
+      <c r="BA7" s="30"/>
+      <c r="BB7" s="31"/>
     </row>
-    <row r="8" spans="1:54" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:54" s="1" customFormat="1">
       <c r="A8" s="38"/>
       <c r="B8" s="39"/>
       <c r="C8" s="39"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="41"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="35"/>
       <c r="G8" s="2">
         <v>1</v>
       </c>
@@ -1706,7 +1708,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:54">
       <c r="A9" s="5">
         <v>1</v>
       </c>
@@ -1804,7 +1806,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:54">
       <c r="A10" s="5">
         <v>2</v>
       </c>
@@ -1904,7 +1906,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:54">
       <c r="A11" s="5">
         <v>3</v>
       </c>
@@ -2002,7 +2004,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:54">
       <c r="A12" s="5">
         <v>4</v>
       </c>
@@ -2100,7 +2102,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:54">
       <c r="A13" s="5">
         <v>5</v>
       </c>
@@ -2198,7 +2200,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:54">
       <c r="A14" s="5">
         <v>6</v>
       </c>
@@ -2294,7 +2296,7 @@
       <c r="BA14" s="9"/>
       <c r="BB14" s="10"/>
     </row>
-    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:54">
       <c r="A15" s="5">
         <v>7</v>
       </c>
@@ -2352,7 +2354,7 @@
       <c r="BA15" s="9"/>
       <c r="BB15" s="10"/>
     </row>
-    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:54">
       <c r="A16" s="5">
         <v>8</v>
       </c>
@@ -2410,7 +2412,7 @@
       <c r="BA16" s="9"/>
       <c r="BB16" s="10"/>
     </row>
-    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:54">
       <c r="A17" s="5">
         <v>9</v>
       </c>
@@ -2468,7 +2470,7 @@
       <c r="BA17" s="9"/>
       <c r="BB17" s="10"/>
     </row>
-    <row r="18" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:54">
       <c r="A18" s="12">
         <v>10</v>
       </c>
@@ -2526,7 +2528,7 @@
       <c r="BA18" s="16"/>
       <c r="BB18" s="17"/>
     </row>
-    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:54">
       <c r="A19" s="5" t="s">
         <v>44</v>
       </c>
@@ -2535,56 +2537,56 @@
       <c r="D19" s="18"/>
       <c r="E19" s="18"/>
       <c r="F19" s="7"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="30"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="25"/>
-      <c r="N19" s="26"/>
-      <c r="O19" s="30"/>
-      <c r="P19" s="25"/>
-      <c r="Q19" s="25"/>
-      <c r="R19" s="26"/>
-      <c r="S19" s="30"/>
-      <c r="T19" s="25"/>
-      <c r="U19" s="25"/>
-      <c r="V19" s="26"/>
-      <c r="W19" s="30"/>
-      <c r="X19" s="25"/>
-      <c r="Y19" s="25"/>
-      <c r="Z19" s="26"/>
-      <c r="AA19" s="30"/>
-      <c r="AB19" s="25"/>
-      <c r="AC19" s="25"/>
-      <c r="AD19" s="26"/>
-      <c r="AE19" s="30"/>
-      <c r="AF19" s="25"/>
-      <c r="AG19" s="25"/>
-      <c r="AH19" s="26"/>
-      <c r="AI19" s="30"/>
-      <c r="AJ19" s="25"/>
-      <c r="AK19" s="25"/>
-      <c r="AL19" s="26"/>
-      <c r="AM19" s="30"/>
-      <c r="AN19" s="25"/>
-      <c r="AO19" s="25"/>
-      <c r="AP19" s="26"/>
-      <c r="AQ19" s="30"/>
-      <c r="AR19" s="25"/>
-      <c r="AS19" s="25"/>
-      <c r="AT19" s="26"/>
-      <c r="AU19" s="30"/>
-      <c r="AV19" s="25"/>
-      <c r="AW19" s="25"/>
-      <c r="AX19" s="26"/>
-      <c r="AY19" s="30"/>
-      <c r="AZ19" s="25"/>
-      <c r="BA19" s="25"/>
-      <c r="BB19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="27"/>
+      <c r="Q19" s="27"/>
+      <c r="R19" s="28"/>
+      <c r="S19" s="26"/>
+      <c r="T19" s="27"/>
+      <c r="U19" s="27"/>
+      <c r="V19" s="28"/>
+      <c r="W19" s="26"/>
+      <c r="X19" s="27"/>
+      <c r="Y19" s="27"/>
+      <c r="Z19" s="28"/>
+      <c r="AA19" s="26"/>
+      <c r="AB19" s="27"/>
+      <c r="AC19" s="27"/>
+      <c r="AD19" s="28"/>
+      <c r="AE19" s="26"/>
+      <c r="AF19" s="27"/>
+      <c r="AG19" s="27"/>
+      <c r="AH19" s="28"/>
+      <c r="AI19" s="26"/>
+      <c r="AJ19" s="27"/>
+      <c r="AK19" s="27"/>
+      <c r="AL19" s="28"/>
+      <c r="AM19" s="26"/>
+      <c r="AN19" s="27"/>
+      <c r="AO19" s="27"/>
+      <c r="AP19" s="28"/>
+      <c r="AQ19" s="26"/>
+      <c r="AR19" s="27"/>
+      <c r="AS19" s="27"/>
+      <c r="AT19" s="28"/>
+      <c r="AU19" s="26"/>
+      <c r="AV19" s="27"/>
+      <c r="AW19" s="27"/>
+      <c r="AX19" s="28"/>
+      <c r="AY19" s="26"/>
+      <c r="AZ19" s="27"/>
+      <c r="BA19" s="27"/>
+      <c r="BB19" s="28"/>
     </row>
-    <row r="20" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:54" ht="15.95" thickBot="1">
       <c r="A20" s="5" t="s">
         <v>45</v>
       </c>
@@ -2593,56 +2595,56 @@
       <c r="D20" s="18"/>
       <c r="E20" s="18"/>
       <c r="F20" s="7"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="27"/>
-      <c r="M20" s="27"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="29"/>
-      <c r="P20" s="27"/>
-      <c r="Q20" s="27"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="27"/>
-      <c r="U20" s="27"/>
-      <c r="V20" s="28"/>
-      <c r="W20" s="29"/>
-      <c r="X20" s="27"/>
-      <c r="Y20" s="27"/>
-      <c r="Z20" s="28"/>
-      <c r="AA20" s="29"/>
-      <c r="AB20" s="27"/>
-      <c r="AC20" s="27"/>
-      <c r="AD20" s="28"/>
-      <c r="AE20" s="29"/>
-      <c r="AF20" s="27"/>
-      <c r="AG20" s="27"/>
-      <c r="AH20" s="28"/>
-      <c r="AI20" s="29"/>
-      <c r="AJ20" s="27"/>
-      <c r="AK20" s="27"/>
-      <c r="AL20" s="28"/>
-      <c r="AM20" s="29"/>
-      <c r="AN20" s="27"/>
-      <c r="AO20" s="27"/>
-      <c r="AP20" s="28"/>
-      <c r="AQ20" s="29"/>
-      <c r="AR20" s="27"/>
-      <c r="AS20" s="27"/>
-      <c r="AT20" s="28"/>
-      <c r="AU20" s="29"/>
-      <c r="AV20" s="27"/>
-      <c r="AW20" s="27"/>
-      <c r="AX20" s="28"/>
-      <c r="AY20" s="29"/>
-      <c r="AZ20" s="27"/>
-      <c r="BA20" s="27"/>
-      <c r="BB20" s="28"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="23"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="23"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="24"/>
+      <c r="R20" s="25"/>
+      <c r="S20" s="23"/>
+      <c r="T20" s="24"/>
+      <c r="U20" s="24"/>
+      <c r="V20" s="25"/>
+      <c r="W20" s="23"/>
+      <c r="X20" s="24"/>
+      <c r="Y20" s="24"/>
+      <c r="Z20" s="25"/>
+      <c r="AA20" s="23"/>
+      <c r="AB20" s="24"/>
+      <c r="AC20" s="24"/>
+      <c r="AD20" s="25"/>
+      <c r="AE20" s="23"/>
+      <c r="AF20" s="24"/>
+      <c r="AG20" s="24"/>
+      <c r="AH20" s="25"/>
+      <c r="AI20" s="23"/>
+      <c r="AJ20" s="24"/>
+      <c r="AK20" s="24"/>
+      <c r="AL20" s="25"/>
+      <c r="AM20" s="23"/>
+      <c r="AN20" s="24"/>
+      <c r="AO20" s="24"/>
+      <c r="AP20" s="25"/>
+      <c r="AQ20" s="23"/>
+      <c r="AR20" s="24"/>
+      <c r="AS20" s="24"/>
+      <c r="AT20" s="25"/>
+      <c r="AU20" s="23"/>
+      <c r="AV20" s="24"/>
+      <c r="AW20" s="24"/>
+      <c r="AX20" s="25"/>
+      <c r="AY20" s="23"/>
+      <c r="AZ20" s="24"/>
+      <c r="BA20" s="24"/>
+      <c r="BB20" s="25"/>
     </row>
-    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:54">
       <c r="A21" s="5" t="s">
         <v>46</v>
       </c>
@@ -2651,56 +2653,56 @@
       <c r="D21" s="19"/>
       <c r="E21" s="19"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
-      <c r="S21" s="23"/>
-      <c r="T21" s="23"/>
-      <c r="U21" s="23"/>
-      <c r="V21" s="23"/>
-      <c r="W21" s="23"/>
-      <c r="X21" s="23"/>
-      <c r="Y21" s="23"/>
-      <c r="Z21" s="23"/>
-      <c r="AA21" s="23"/>
-      <c r="AB21" s="23"/>
-      <c r="AC21" s="23"/>
-      <c r="AD21" s="23"/>
-      <c r="AE21" s="23"/>
-      <c r="AF21" s="23"/>
-      <c r="AG21" s="23"/>
-      <c r="AH21" s="23"/>
-      <c r="AI21" s="23"/>
-      <c r="AJ21" s="23"/>
-      <c r="AK21" s="23"/>
-      <c r="AL21" s="23"/>
-      <c r="AM21" s="23"/>
-      <c r="AN21" s="23"/>
-      <c r="AO21" s="23"/>
-      <c r="AP21" s="23"/>
-      <c r="AQ21" s="23"/>
-      <c r="AR21" s="23"/>
-      <c r="AS21" s="23"/>
-      <c r="AT21" s="23"/>
-      <c r="AU21" s="23"/>
-      <c r="AV21" s="23"/>
-      <c r="AW21" s="23"/>
-      <c r="AX21" s="23"/>
-      <c r="AY21" s="23"/>
-      <c r="AZ21" s="23"/>
-      <c r="BA21" s="23"/>
-      <c r="BB21" s="24"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32"/>
+      <c r="N21" s="32"/>
+      <c r="O21" s="32"/>
+      <c r="P21" s="32"/>
+      <c r="Q21" s="32"/>
+      <c r="R21" s="32"/>
+      <c r="S21" s="32"/>
+      <c r="T21" s="32"/>
+      <c r="U21" s="32"/>
+      <c r="V21" s="32"/>
+      <c r="W21" s="32"/>
+      <c r="X21" s="32"/>
+      <c r="Y21" s="32"/>
+      <c r="Z21" s="32"/>
+      <c r="AA21" s="32"/>
+      <c r="AB21" s="32"/>
+      <c r="AC21" s="32"/>
+      <c r="AD21" s="32"/>
+      <c r="AE21" s="32"/>
+      <c r="AF21" s="32"/>
+      <c r="AG21" s="32"/>
+      <c r="AH21" s="32"/>
+      <c r="AI21" s="32"/>
+      <c r="AJ21" s="32"/>
+      <c r="AK21" s="32"/>
+      <c r="AL21" s="32"/>
+      <c r="AM21" s="32"/>
+      <c r="AN21" s="32"/>
+      <c r="AO21" s="32"/>
+      <c r="AP21" s="32"/>
+      <c r="AQ21" s="32"/>
+      <c r="AR21" s="32"/>
+      <c r="AS21" s="32"/>
+      <c r="AT21" s="32"/>
+      <c r="AU21" s="32"/>
+      <c r="AV21" s="32"/>
+      <c r="AW21" s="32"/>
+      <c r="AX21" s="32"/>
+      <c r="AY21" s="32"/>
+      <c r="AZ21" s="32"/>
+      <c r="BA21" s="32"/>
+      <c r="BB21" s="33"/>
     </row>
-    <row r="22" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:54">
       <c r="A22" s="5" t="s">
         <v>47</v>
       </c>
@@ -2709,56 +2711,56 @@
       <c r="D22" s="19"/>
       <c r="E22" s="19"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="25"/>
-      <c r="L22" s="25"/>
-      <c r="M22" s="25"/>
-      <c r="N22" s="25"/>
-      <c r="O22" s="25"/>
-      <c r="P22" s="25"/>
-      <c r="Q22" s="25"/>
-      <c r="R22" s="25"/>
-      <c r="S22" s="25"/>
-      <c r="T22" s="25"/>
-      <c r="U22" s="25"/>
-      <c r="V22" s="25"/>
-      <c r="W22" s="25"/>
-      <c r="X22" s="25"/>
-      <c r="Y22" s="25"/>
-      <c r="Z22" s="25"/>
-      <c r="AA22" s="25"/>
-      <c r="AB22" s="25"/>
-      <c r="AC22" s="25"/>
-      <c r="AD22" s="25"/>
-      <c r="AE22" s="25"/>
-      <c r="AF22" s="25"/>
-      <c r="AG22" s="25"/>
-      <c r="AH22" s="25"/>
-      <c r="AI22" s="25"/>
-      <c r="AJ22" s="25"/>
-      <c r="AK22" s="25"/>
-      <c r="AL22" s="25"/>
-      <c r="AM22" s="25"/>
-      <c r="AN22" s="25"/>
-      <c r="AO22" s="25"/>
-      <c r="AP22" s="25"/>
-      <c r="AQ22" s="25"/>
-      <c r="AR22" s="25"/>
-      <c r="AS22" s="25"/>
-      <c r="AT22" s="25"/>
-      <c r="AU22" s="25"/>
-      <c r="AV22" s="25"/>
-      <c r="AW22" s="25"/>
-      <c r="AX22" s="25"/>
-      <c r="AY22" s="25"/>
-      <c r="AZ22" s="25"/>
-      <c r="BA22" s="25"/>
-      <c r="BB22" s="26"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="27"/>
+      <c r="K22" s="27"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="27"/>
+      <c r="N22" s="27"/>
+      <c r="O22" s="27"/>
+      <c r="P22" s="27"/>
+      <c r="Q22" s="27"/>
+      <c r="R22" s="27"/>
+      <c r="S22" s="27"/>
+      <c r="T22" s="27"/>
+      <c r="U22" s="27"/>
+      <c r="V22" s="27"/>
+      <c r="W22" s="27"/>
+      <c r="X22" s="27"/>
+      <c r="Y22" s="27"/>
+      <c r="Z22" s="27"/>
+      <c r="AA22" s="27"/>
+      <c r="AB22" s="27"/>
+      <c r="AC22" s="27"/>
+      <c r="AD22" s="27"/>
+      <c r="AE22" s="27"/>
+      <c r="AF22" s="27"/>
+      <c r="AG22" s="27"/>
+      <c r="AH22" s="27"/>
+      <c r="AI22" s="27"/>
+      <c r="AJ22" s="27"/>
+      <c r="AK22" s="27"/>
+      <c r="AL22" s="27"/>
+      <c r="AM22" s="27"/>
+      <c r="AN22" s="27"/>
+      <c r="AO22" s="27"/>
+      <c r="AP22" s="27"/>
+      <c r="AQ22" s="27"/>
+      <c r="AR22" s="27"/>
+      <c r="AS22" s="27"/>
+      <c r="AT22" s="27"/>
+      <c r="AU22" s="27"/>
+      <c r="AV22" s="27"/>
+      <c r="AW22" s="27"/>
+      <c r="AX22" s="27"/>
+      <c r="AY22" s="27"/>
+      <c r="AZ22" s="27"/>
+      <c r="BA22" s="27"/>
+      <c r="BB22" s="28"/>
     </row>
-    <row r="23" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:54" ht="15.95" thickBot="1">
       <c r="A23" s="20" t="s">
         <v>48</v>
       </c>
@@ -2767,69 +2769,100 @@
       <c r="D23" s="21"/>
       <c r="E23" s="21"/>
       <c r="F23" s="22"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="P23" s="27"/>
-      <c r="Q23" s="27"/>
-      <c r="R23" s="27"/>
-      <c r="S23" s="27"/>
-      <c r="T23" s="27"/>
-      <c r="U23" s="27"/>
-      <c r="V23" s="27"/>
-      <c r="W23" s="27"/>
-      <c r="X23" s="27"/>
-      <c r="Y23" s="27"/>
-      <c r="Z23" s="27"/>
-      <c r="AA23" s="27"/>
-      <c r="AB23" s="27"/>
-      <c r="AC23" s="27"/>
-      <c r="AD23" s="27"/>
-      <c r="AE23" s="27"/>
-      <c r="AF23" s="27"/>
-      <c r="AG23" s="27"/>
-      <c r="AH23" s="27"/>
-      <c r="AI23" s="27"/>
-      <c r="AJ23" s="27"/>
-      <c r="AK23" s="27"/>
-      <c r="AL23" s="27"/>
-      <c r="AM23" s="27"/>
-      <c r="AN23" s="27"/>
-      <c r="AO23" s="27"/>
-      <c r="AP23" s="27"/>
-      <c r="AQ23" s="27"/>
-      <c r="AR23" s="27"/>
-      <c r="AS23" s="27"/>
-      <c r="AT23" s="27"/>
-      <c r="AU23" s="27"/>
-      <c r="AV23" s="27"/>
-      <c r="AW23" s="27"/>
-      <c r="AX23" s="27"/>
-      <c r="AY23" s="27"/>
-      <c r="AZ23" s="27"/>
-      <c r="BA23" s="27"/>
-      <c r="BB23" s="28"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
+      <c r="N23" s="24"/>
+      <c r="O23" s="24"/>
+      <c r="P23" s="24"/>
+      <c r="Q23" s="24"/>
+      <c r="R23" s="24"/>
+      <c r="S23" s="24"/>
+      <c r="T23" s="24"/>
+      <c r="U23" s="24"/>
+      <c r="V23" s="24"/>
+      <c r="W23" s="24"/>
+      <c r="X23" s="24"/>
+      <c r="Y23" s="24"/>
+      <c r="Z23" s="24"/>
+      <c r="AA23" s="24"/>
+      <c r="AB23" s="24"/>
+      <c r="AC23" s="24"/>
+      <c r="AD23" s="24"/>
+      <c r="AE23" s="24"/>
+      <c r="AF23" s="24"/>
+      <c r="AG23" s="24"/>
+      <c r="AH23" s="24"/>
+      <c r="AI23" s="24"/>
+      <c r="AJ23" s="24"/>
+      <c r="AK23" s="24"/>
+      <c r="AL23" s="24"/>
+      <c r="AM23" s="24"/>
+      <c r="AN23" s="24"/>
+      <c r="AO23" s="24"/>
+      <c r="AP23" s="24"/>
+      <c r="AQ23" s="24"/>
+      <c r="AR23" s="24"/>
+      <c r="AS23" s="24"/>
+      <c r="AT23" s="24"/>
+      <c r="AU23" s="24"/>
+      <c r="AV23" s="24"/>
+      <c r="AW23" s="24"/>
+      <c r="AX23" s="24"/>
+      <c r="AY23" s="24"/>
+      <c r="AZ23" s="24"/>
+      <c r="BA23" s="24"/>
+      <c r="BB23" s="25"/>
     </row>
-    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:54">
       <c r="A24" s="1" t="s">
         <v>49</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="G4:BB4"/>
-    <mergeCell ref="A1:BB1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:BB2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="G3:BB3"/>
+    <mergeCell ref="G21:AD21"/>
+    <mergeCell ref="AE21:BB21"/>
+    <mergeCell ref="G22:AD22"/>
+    <mergeCell ref="AE22:BB22"/>
+    <mergeCell ref="G23:AD23"/>
+    <mergeCell ref="AE23:BB23"/>
+    <mergeCell ref="AY20:BB20"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="K20:N20"/>
+    <mergeCell ref="O20:R20"/>
+    <mergeCell ref="S20:V20"/>
+    <mergeCell ref="W20:Z20"/>
+    <mergeCell ref="AA20:AD20"/>
+    <mergeCell ref="AE20:AH20"/>
+    <mergeCell ref="AI20:AL20"/>
+    <mergeCell ref="AM20:AP20"/>
+    <mergeCell ref="AQ20:AT20"/>
+    <mergeCell ref="AU20:AX20"/>
+    <mergeCell ref="AE19:AH19"/>
+    <mergeCell ref="AI19:AL19"/>
+    <mergeCell ref="AM19:AP19"/>
+    <mergeCell ref="AQ19:AT19"/>
+    <mergeCell ref="AU19:AX19"/>
+    <mergeCell ref="AY19:BB19"/>
+    <mergeCell ref="AM7:AP7"/>
+    <mergeCell ref="AQ7:AT7"/>
+    <mergeCell ref="AU7:AX7"/>
+    <mergeCell ref="AY7:BB7"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="K19:N19"/>
+    <mergeCell ref="O19:R19"/>
+    <mergeCell ref="S19:V19"/>
+    <mergeCell ref="W19:Z19"/>
+    <mergeCell ref="AA19:AD19"/>
+    <mergeCell ref="O7:R7"/>
+    <mergeCell ref="S7:V7"/>
+    <mergeCell ref="W7:Z7"/>
+    <mergeCell ref="AA7:AD7"/>
     <mergeCell ref="AE7:AH7"/>
     <mergeCell ref="AI7:AL7"/>
     <mergeCell ref="A5:BB5"/>
@@ -2842,44 +2875,13 @@
     <mergeCell ref="G6:BB6"/>
     <mergeCell ref="G7:J7"/>
     <mergeCell ref="K7:N7"/>
-    <mergeCell ref="AA19:AD19"/>
-    <mergeCell ref="O7:R7"/>
-    <mergeCell ref="S7:V7"/>
-    <mergeCell ref="W7:Z7"/>
-    <mergeCell ref="AA7:AD7"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="K19:N19"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="S19:V19"/>
-    <mergeCell ref="W19:Z19"/>
-    <mergeCell ref="AY19:BB19"/>
-    <mergeCell ref="AM7:AP7"/>
-    <mergeCell ref="AQ7:AT7"/>
-    <mergeCell ref="AU7:AX7"/>
-    <mergeCell ref="AY7:BB7"/>
-    <mergeCell ref="AE19:AH19"/>
-    <mergeCell ref="AI19:AL19"/>
-    <mergeCell ref="AM19:AP19"/>
-    <mergeCell ref="AQ19:AT19"/>
-    <mergeCell ref="AU19:AX19"/>
-    <mergeCell ref="AY20:BB20"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="K20:N20"/>
-    <mergeCell ref="O20:R20"/>
-    <mergeCell ref="S20:V20"/>
-    <mergeCell ref="W20:Z20"/>
-    <mergeCell ref="AA20:AD20"/>
-    <mergeCell ref="AE20:AH20"/>
-    <mergeCell ref="AI20:AL20"/>
-    <mergeCell ref="AM20:AP20"/>
-    <mergeCell ref="AQ20:AT20"/>
-    <mergeCell ref="AU20:AX20"/>
-    <mergeCell ref="G21:AD21"/>
-    <mergeCell ref="AE21:BB21"/>
-    <mergeCell ref="G22:AD22"/>
-    <mergeCell ref="AE22:BB22"/>
-    <mergeCell ref="G23:AD23"/>
-    <mergeCell ref="AE23:BB23"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="G4:BB4"/>
+    <mergeCell ref="A1:BB1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="G2:BB2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="G3:BB3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2889,308 +2891,308 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C388B2CD-30CB-43A1-A21B-BE31D13F92F7}">
   <dimension ref="A1:BB24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="14.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="27.28515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" style="1" customWidth="1"/>
     <col min="6" max="6" width="27.85546875" customWidth="1"/>
     <col min="7" max="54" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
+    <row r="1" spans="1:54" ht="35.25" customHeight="1">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="47"/>
-      <c r="S1" s="47"/>
-      <c r="T1" s="47"/>
-      <c r="U1" s="47"/>
-      <c r="V1" s="47"/>
-      <c r="W1" s="47"/>
-      <c r="X1" s="47"/>
-      <c r="Y1" s="47"/>
-      <c r="Z1" s="47"/>
-      <c r="AA1" s="47"/>
-      <c r="AB1" s="47"/>
-      <c r="AC1" s="47"/>
-      <c r="AD1" s="47"/>
-      <c r="AE1" s="47"/>
-      <c r="AF1" s="47"/>
-      <c r="AG1" s="47"/>
-      <c r="AH1" s="47"/>
-      <c r="AI1" s="47"/>
-      <c r="AJ1" s="47"/>
-      <c r="AK1" s="47"/>
-      <c r="AL1" s="47"/>
-      <c r="AM1" s="47"/>
-      <c r="AN1" s="47"/>
-      <c r="AO1" s="47"/>
-      <c r="AP1" s="47"/>
-      <c r="AQ1" s="47"/>
-      <c r="AR1" s="47"/>
-      <c r="AS1" s="47"/>
-      <c r="AT1" s="47"/>
-      <c r="AU1" s="47"/>
-      <c r="AV1" s="47"/>
-      <c r="AW1" s="47"/>
-      <c r="AX1" s="47"/>
-      <c r="AY1" s="47"/>
-      <c r="AZ1" s="47"/>
-      <c r="BA1" s="47"/>
-      <c r="BB1" s="48"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="43"/>
+      <c r="W1" s="43"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="43"/>
+      <c r="AA1" s="43"/>
+      <c r="AB1" s="43"/>
+      <c r="AC1" s="43"/>
+      <c r="AD1" s="43"/>
+      <c r="AE1" s="43"/>
+      <c r="AF1" s="43"/>
+      <c r="AG1" s="43"/>
+      <c r="AH1" s="43"/>
+      <c r="AI1" s="43"/>
+      <c r="AJ1" s="43"/>
+      <c r="AK1" s="43"/>
+      <c r="AL1" s="43"/>
+      <c r="AM1" s="43"/>
+      <c r="AN1" s="43"/>
+      <c r="AO1" s="43"/>
+      <c r="AP1" s="43"/>
+      <c r="AQ1" s="43"/>
+      <c r="AR1" s="43"/>
+      <c r="AS1" s="43"/>
+      <c r="AT1" s="43"/>
+      <c r="AU1" s="43"/>
+      <c r="AV1" s="43"/>
+      <c r="AW1" s="43"/>
+      <c r="AX1" s="43"/>
+      <c r="AY1" s="43"/>
+      <c r="AZ1" s="43"/>
+      <c r="BA1" s="43"/>
+      <c r="BB1" s="44"/>
     </row>
-    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A2" s="49" t="s">
+    <row r="2" spans="1:54">
+      <c r="A2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="25"/>
-      <c r="Z2" s="25"/>
-      <c r="AA2" s="25"/>
-      <c r="AB2" s="25"/>
-      <c r="AC2" s="25"/>
-      <c r="AD2" s="25"/>
-      <c r="AE2" s="25"/>
-      <c r="AF2" s="25"/>
-      <c r="AG2" s="25"/>
-      <c r="AH2" s="25"/>
-      <c r="AI2" s="25"/>
-      <c r="AJ2" s="25"/>
-      <c r="AK2" s="25"/>
-      <c r="AL2" s="25"/>
-      <c r="AM2" s="25"/>
-      <c r="AN2" s="25"/>
-      <c r="AO2" s="25"/>
-      <c r="AP2" s="25"/>
-      <c r="AQ2" s="25"/>
-      <c r="AR2" s="25"/>
-      <c r="AS2" s="25"/>
-      <c r="AT2" s="25"/>
-      <c r="AU2" s="25"/>
-      <c r="AV2" s="25"/>
-      <c r="AW2" s="25"/>
-      <c r="AX2" s="25"/>
-      <c r="AY2" s="25"/>
-      <c r="AZ2" s="25"/>
-      <c r="BA2" s="25"/>
-      <c r="BB2" s="26"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+      <c r="V2" s="27"/>
+      <c r="W2" s="27"/>
+      <c r="X2" s="27"/>
+      <c r="Y2" s="27"/>
+      <c r="Z2" s="27"/>
+      <c r="AA2" s="27"/>
+      <c r="AB2" s="27"/>
+      <c r="AC2" s="27"/>
+      <c r="AD2" s="27"/>
+      <c r="AE2" s="27"/>
+      <c r="AF2" s="27"/>
+      <c r="AG2" s="27"/>
+      <c r="AH2" s="27"/>
+      <c r="AI2" s="27"/>
+      <c r="AJ2" s="27"/>
+      <c r="AK2" s="27"/>
+      <c r="AL2" s="27"/>
+      <c r="AM2" s="27"/>
+      <c r="AN2" s="27"/>
+      <c r="AO2" s="27"/>
+      <c r="AP2" s="27"/>
+      <c r="AQ2" s="27"/>
+      <c r="AR2" s="27"/>
+      <c r="AS2" s="27"/>
+      <c r="AT2" s="27"/>
+      <c r="AU2" s="27"/>
+      <c r="AV2" s="27"/>
+      <c r="AW2" s="27"/>
+      <c r="AX2" s="27"/>
+      <c r="AY2" s="27"/>
+      <c r="AZ2" s="27"/>
+      <c r="BA2" s="27"/>
+      <c r="BB2" s="28"/>
     </row>
-    <row r="3" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
+    <row r="3" spans="1:54">
+      <c r="A3" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="25"/>
-      <c r="X3" s="25"/>
-      <c r="Y3" s="25"/>
-      <c r="Z3" s="25"/>
-      <c r="AA3" s="25"/>
-      <c r="AB3" s="25"/>
-      <c r="AC3" s="25"/>
-      <c r="AD3" s="25"/>
-      <c r="AE3" s="25"/>
-      <c r="AF3" s="25"/>
-      <c r="AG3" s="25"/>
-      <c r="AH3" s="25"/>
-      <c r="AI3" s="25"/>
-      <c r="AJ3" s="25"/>
-      <c r="AK3" s="25"/>
-      <c r="AL3" s="25"/>
-      <c r="AM3" s="25"/>
-      <c r="AN3" s="25"/>
-      <c r="AO3" s="25"/>
-      <c r="AP3" s="25"/>
-      <c r="AQ3" s="25"/>
-      <c r="AR3" s="25"/>
-      <c r="AS3" s="25"/>
-      <c r="AT3" s="25"/>
-      <c r="AU3" s="25"/>
-      <c r="AV3" s="25"/>
-      <c r="AW3" s="25"/>
-      <c r="AX3" s="25"/>
-      <c r="AY3" s="25"/>
-      <c r="AZ3" s="25"/>
-      <c r="BA3" s="25"/>
-      <c r="BB3" s="26"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="27"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="27"/>
+      <c r="V3" s="27"/>
+      <c r="W3" s="27"/>
+      <c r="X3" s="27"/>
+      <c r="Y3" s="27"/>
+      <c r="Z3" s="27"/>
+      <c r="AA3" s="27"/>
+      <c r="AB3" s="27"/>
+      <c r="AC3" s="27"/>
+      <c r="AD3" s="27"/>
+      <c r="AE3" s="27"/>
+      <c r="AF3" s="27"/>
+      <c r="AG3" s="27"/>
+      <c r="AH3" s="27"/>
+      <c r="AI3" s="27"/>
+      <c r="AJ3" s="27"/>
+      <c r="AK3" s="27"/>
+      <c r="AL3" s="27"/>
+      <c r="AM3" s="27"/>
+      <c r="AN3" s="27"/>
+      <c r="AO3" s="27"/>
+      <c r="AP3" s="27"/>
+      <c r="AQ3" s="27"/>
+      <c r="AR3" s="27"/>
+      <c r="AS3" s="27"/>
+      <c r="AT3" s="27"/>
+      <c r="AU3" s="27"/>
+      <c r="AV3" s="27"/>
+      <c r="AW3" s="27"/>
+      <c r="AX3" s="27"/>
+      <c r="AY3" s="27"/>
+      <c r="AZ3" s="27"/>
+      <c r="BA3" s="27"/>
+      <c r="BB3" s="28"/>
     </row>
-    <row r="4" spans="1:54" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
+    <row r="4" spans="1:54" ht="52.5" customHeight="1">
+      <c r="A4" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="56"/>
-      <c r="Q4" s="56"/>
-      <c r="R4" s="56"/>
-      <c r="S4" s="56"/>
-      <c r="T4" s="56"/>
-      <c r="U4" s="56"/>
-      <c r="V4" s="56"/>
-      <c r="W4" s="56"/>
-      <c r="X4" s="56"/>
-      <c r="Y4" s="56"/>
-      <c r="Z4" s="56"/>
-      <c r="AA4" s="56"/>
-      <c r="AB4" s="56"/>
-      <c r="AC4" s="56"/>
-      <c r="AD4" s="56"/>
-      <c r="AE4" s="56"/>
-      <c r="AF4" s="56"/>
-      <c r="AG4" s="56"/>
-      <c r="AH4" s="56"/>
-      <c r="AI4" s="56"/>
-      <c r="AJ4" s="56"/>
-      <c r="AK4" s="56"/>
-      <c r="AL4" s="56"/>
-      <c r="AM4" s="56"/>
-      <c r="AN4" s="56"/>
-      <c r="AO4" s="56"/>
-      <c r="AP4" s="56"/>
-      <c r="AQ4" s="56"/>
-      <c r="AR4" s="56"/>
-      <c r="AS4" s="56"/>
-      <c r="AT4" s="56"/>
-      <c r="AU4" s="56"/>
-      <c r="AV4" s="56"/>
-      <c r="AW4" s="56"/>
-      <c r="AX4" s="56"/>
-      <c r="AY4" s="56"/>
-      <c r="AZ4" s="56"/>
-      <c r="BA4" s="56"/>
-      <c r="BB4" s="57"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="52"/>
+      <c r="N4" s="52"/>
+      <c r="O4" s="52"/>
+      <c r="P4" s="52"/>
+      <c r="Q4" s="52"/>
+      <c r="R4" s="52"/>
+      <c r="S4" s="52"/>
+      <c r="T4" s="52"/>
+      <c r="U4" s="52"/>
+      <c r="V4" s="52"/>
+      <c r="W4" s="52"/>
+      <c r="X4" s="52"/>
+      <c r="Y4" s="52"/>
+      <c r="Z4" s="52"/>
+      <c r="AA4" s="52"/>
+      <c r="AB4" s="52"/>
+      <c r="AC4" s="52"/>
+      <c r="AD4" s="52"/>
+      <c r="AE4" s="52"/>
+      <c r="AF4" s="52"/>
+      <c r="AG4" s="52"/>
+      <c r="AH4" s="52"/>
+      <c r="AI4" s="52"/>
+      <c r="AJ4" s="52"/>
+      <c r="AK4" s="52"/>
+      <c r="AL4" s="52"/>
+      <c r="AM4" s="52"/>
+      <c r="AN4" s="52"/>
+      <c r="AO4" s="52"/>
+      <c r="AP4" s="52"/>
+      <c r="AQ4" s="52"/>
+      <c r="AR4" s="52"/>
+      <c r="AS4" s="52"/>
+      <c r="AT4" s="52"/>
+      <c r="AU4" s="52"/>
+      <c r="AV4" s="52"/>
+      <c r="AW4" s="52"/>
+      <c r="AX4" s="52"/>
+      <c r="AY4" s="52"/>
+      <c r="AZ4" s="52"/>
+      <c r="BA4" s="52"/>
+      <c r="BB4" s="53"/>
     </row>
-    <row r="5" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
+    <row r="5" spans="1:54">
+      <c r="A5" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
-      <c r="S5" s="36"/>
-      <c r="T5" s="36"/>
-      <c r="U5" s="36"/>
-      <c r="V5" s="36"/>
-      <c r="W5" s="36"/>
-      <c r="X5" s="36"/>
-      <c r="Y5" s="36"/>
-      <c r="Z5" s="36"/>
-      <c r="AA5" s="36"/>
-      <c r="AB5" s="36"/>
-      <c r="AC5" s="36"/>
-      <c r="AD5" s="36"/>
-      <c r="AE5" s="36"/>
-      <c r="AF5" s="36"/>
-      <c r="AG5" s="36"/>
-      <c r="AH5" s="36"/>
-      <c r="AI5" s="36"/>
-      <c r="AJ5" s="36"/>
-      <c r="AK5" s="36"/>
-      <c r="AL5" s="36"/>
-      <c r="AM5" s="36"/>
-      <c r="AN5" s="36"/>
-      <c r="AO5" s="36"/>
-      <c r="AP5" s="36"/>
-      <c r="AQ5" s="36"/>
-      <c r="AR5" s="36"/>
-      <c r="AS5" s="36"/>
-      <c r="AT5" s="36"/>
-      <c r="AU5" s="36"/>
-      <c r="AV5" s="36"/>
-      <c r="AW5" s="36"/>
-      <c r="AX5" s="36"/>
-      <c r="AY5" s="36"/>
-      <c r="AZ5" s="36"/>
-      <c r="BA5" s="36"/>
-      <c r="BB5" s="37"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="56"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="56"/>
+      <c r="P5" s="56"/>
+      <c r="Q5" s="56"/>
+      <c r="R5" s="56"/>
+      <c r="S5" s="56"/>
+      <c r="T5" s="56"/>
+      <c r="U5" s="56"/>
+      <c r="V5" s="56"/>
+      <c r="W5" s="56"/>
+      <c r="X5" s="56"/>
+      <c r="Y5" s="56"/>
+      <c r="Z5" s="56"/>
+      <c r="AA5" s="56"/>
+      <c r="AB5" s="56"/>
+      <c r="AC5" s="56"/>
+      <c r="AD5" s="56"/>
+      <c r="AE5" s="56"/>
+      <c r="AF5" s="56"/>
+      <c r="AG5" s="56"/>
+      <c r="AH5" s="56"/>
+      <c r="AI5" s="56"/>
+      <c r="AJ5" s="56"/>
+      <c r="AK5" s="56"/>
+      <c r="AL5" s="56"/>
+      <c r="AM5" s="56"/>
+      <c r="AN5" s="56"/>
+      <c r="AO5" s="56"/>
+      <c r="AP5" s="56"/>
+      <c r="AQ5" s="56"/>
+      <c r="AR5" s="56"/>
+      <c r="AS5" s="56"/>
+      <c r="AT5" s="56"/>
+      <c r="AU5" s="56"/>
+      <c r="AV5" s="56"/>
+      <c r="AW5" s="56"/>
+      <c r="AX5" s="56"/>
+      <c r="AY5" s="56"/>
+      <c r="AZ5" s="56"/>
+      <c r="BA5" s="56"/>
+      <c r="BB5" s="57"/>
     </row>
-    <row r="6" spans="1:54" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:54" s="1" customFormat="1" ht="15.95" thickBot="1">
       <c r="A6" s="38" t="s">
         <v>7</v>
       </c>
@@ -3200,153 +3202,153 @@
       <c r="C6" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="34" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="40" t="s">
+      <c r="F6" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="43" t="s">
+      <c r="G6" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="43"/>
-      <c r="L6" s="43"/>
-      <c r="M6" s="43"/>
-      <c r="N6" s="43"/>
-      <c r="O6" s="43"/>
-      <c r="P6" s="43"/>
-      <c r="Q6" s="43"/>
-      <c r="R6" s="43"/>
-      <c r="S6" s="43"/>
-      <c r="T6" s="43"/>
-      <c r="U6" s="43"/>
-      <c r="V6" s="43"/>
-      <c r="W6" s="43"/>
-      <c r="X6" s="43"/>
-      <c r="Y6" s="43"/>
-      <c r="Z6" s="43"/>
-      <c r="AA6" s="43"/>
-      <c r="AB6" s="43"/>
-      <c r="AC6" s="43"/>
-      <c r="AD6" s="43"/>
-      <c r="AE6" s="43"/>
-      <c r="AF6" s="43"/>
-      <c r="AG6" s="43"/>
-      <c r="AH6" s="43"/>
-      <c r="AI6" s="43"/>
-      <c r="AJ6" s="43"/>
-      <c r="AK6" s="43"/>
-      <c r="AL6" s="43"/>
-      <c r="AM6" s="43"/>
-      <c r="AN6" s="43"/>
-      <c r="AO6" s="43"/>
-      <c r="AP6" s="43"/>
-      <c r="AQ6" s="43"/>
-      <c r="AR6" s="43"/>
-      <c r="AS6" s="43"/>
-      <c r="AT6" s="43"/>
-      <c r="AU6" s="43"/>
-      <c r="AV6" s="43"/>
-      <c r="AW6" s="43"/>
-      <c r="AX6" s="43"/>
-      <c r="AY6" s="43"/>
-      <c r="AZ6" s="43"/>
-      <c r="BA6" s="43"/>
-      <c r="BB6" s="44"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36"/>
+      <c r="T6" s="36"/>
+      <c r="U6" s="36"/>
+      <c r="V6" s="36"/>
+      <c r="W6" s="36"/>
+      <c r="X6" s="36"/>
+      <c r="Y6" s="36"/>
+      <c r="Z6" s="36"/>
+      <c r="AA6" s="36"/>
+      <c r="AB6" s="36"/>
+      <c r="AC6" s="36"/>
+      <c r="AD6" s="36"/>
+      <c r="AE6" s="36"/>
+      <c r="AF6" s="36"/>
+      <c r="AG6" s="36"/>
+      <c r="AH6" s="36"/>
+      <c r="AI6" s="36"/>
+      <c r="AJ6" s="36"/>
+      <c r="AK6" s="36"/>
+      <c r="AL6" s="36"/>
+      <c r="AM6" s="36"/>
+      <c r="AN6" s="36"/>
+      <c r="AO6" s="36"/>
+      <c r="AP6" s="36"/>
+      <c r="AQ6" s="36"/>
+      <c r="AR6" s="36"/>
+      <c r="AS6" s="36"/>
+      <c r="AT6" s="36"/>
+      <c r="AU6" s="36"/>
+      <c r="AV6" s="36"/>
+      <c r="AW6" s="36"/>
+      <c r="AX6" s="36"/>
+      <c r="AY6" s="36"/>
+      <c r="AZ6" s="36"/>
+      <c r="BA6" s="36"/>
+      <c r="BB6" s="37"/>
     </row>
-    <row r="7" spans="1:54" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:54" s="1" customFormat="1">
       <c r="A7" s="38"/>
       <c r="B7" s="39"/>
       <c r="C7" s="39"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="31" t="s">
+      <c r="D7" s="35"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="31" t="s">
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="L7" s="32"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="33"/>
-      <c r="O7" s="31" t="s">
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="P7" s="32"/>
-      <c r="Q7" s="32"/>
-      <c r="R7" s="33"/>
-      <c r="S7" s="31" t="s">
+      <c r="P7" s="30"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="31"/>
+      <c r="S7" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="T7" s="32"/>
-      <c r="U7" s="32"/>
-      <c r="V7" s="33"/>
-      <c r="W7" s="31" t="s">
+      <c r="T7" s="30"/>
+      <c r="U7" s="30"/>
+      <c r="V7" s="31"/>
+      <c r="W7" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="X7" s="32"/>
-      <c r="Y7" s="32"/>
-      <c r="Z7" s="33"/>
-      <c r="AA7" s="31" t="s">
+      <c r="X7" s="30"/>
+      <c r="Y7" s="30"/>
+      <c r="Z7" s="31"/>
+      <c r="AA7" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="AB7" s="32"/>
-      <c r="AC7" s="32"/>
-      <c r="AD7" s="33"/>
-      <c r="AE7" s="31" t="s">
+      <c r="AB7" s="30"/>
+      <c r="AC7" s="30"/>
+      <c r="AD7" s="31"/>
+      <c r="AE7" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="AF7" s="32"/>
-      <c r="AG7" s="32"/>
-      <c r="AH7" s="33"/>
-      <c r="AI7" s="31" t="s">
+      <c r="AF7" s="30"/>
+      <c r="AG7" s="30"/>
+      <c r="AH7" s="31"/>
+      <c r="AI7" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="AJ7" s="32"/>
-      <c r="AK7" s="32"/>
-      <c r="AL7" s="33"/>
-      <c r="AM7" s="31" t="s">
+      <c r="AJ7" s="30"/>
+      <c r="AK7" s="30"/>
+      <c r="AL7" s="31"/>
+      <c r="AM7" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="AN7" s="32"/>
-      <c r="AO7" s="32"/>
-      <c r="AP7" s="33"/>
-      <c r="AQ7" s="31" t="s">
+      <c r="AN7" s="30"/>
+      <c r="AO7" s="30"/>
+      <c r="AP7" s="31"/>
+      <c r="AQ7" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="AR7" s="32"/>
-      <c r="AS7" s="32"/>
-      <c r="AT7" s="33"/>
-      <c r="AU7" s="31" t="s">
+      <c r="AR7" s="30"/>
+      <c r="AS7" s="30"/>
+      <c r="AT7" s="31"/>
+      <c r="AU7" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="AV7" s="32"/>
-      <c r="AW7" s="32"/>
-      <c r="AX7" s="33"/>
-      <c r="AY7" s="31" t="s">
+      <c r="AV7" s="30"/>
+      <c r="AW7" s="30"/>
+      <c r="AX7" s="31"/>
+      <c r="AY7" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="AZ7" s="32"/>
-      <c r="BA7" s="32"/>
-      <c r="BB7" s="33"/>
+      <c r="AZ7" s="30"/>
+      <c r="BA7" s="30"/>
+      <c r="BB7" s="31"/>
     </row>
-    <row r="8" spans="1:54" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:54" s="1" customFormat="1">
       <c r="A8" s="38"/>
       <c r="B8" s="39"/>
       <c r="C8" s="39"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="41"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="35"/>
       <c r="G8" s="2">
         <v>1</v>
       </c>
@@ -3492,7 +3494,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:54">
       <c r="A9" s="5">
         <v>1</v>
       </c>
@@ -3550,7 +3552,7 @@
       <c r="BA9" s="9"/>
       <c r="BB9" s="10"/>
     </row>
-    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:54">
       <c r="A10" s="5">
         <v>2</v>
       </c>
@@ -3608,7 +3610,7 @@
       <c r="BA10" s="9"/>
       <c r="BB10" s="10"/>
     </row>
-    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:54">
       <c r="A11" s="5">
         <v>3</v>
       </c>
@@ -3666,7 +3668,7 @@
       <c r="BA11" s="9"/>
       <c r="BB11" s="10"/>
     </row>
-    <row r="12" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:54">
       <c r="A12" s="5">
         <v>4</v>
       </c>
@@ -3724,7 +3726,7 @@
       <c r="BA12" s="9"/>
       <c r="BB12" s="10"/>
     </row>
-    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:54">
       <c r="A13" s="5">
         <v>5</v>
       </c>
@@ -3782,7 +3784,7 @@
       <c r="BA13" s="9"/>
       <c r="BB13" s="10"/>
     </row>
-    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:54">
       <c r="A14" s="5">
         <v>6</v>
       </c>
@@ -3840,7 +3842,7 @@
       <c r="BA14" s="9"/>
       <c r="BB14" s="10"/>
     </row>
-    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:54">
       <c r="A15" s="5">
         <v>7</v>
       </c>
@@ -3898,7 +3900,7 @@
       <c r="BA15" s="9"/>
       <c r="BB15" s="10"/>
     </row>
-    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:54">
       <c r="A16" s="5">
         <v>8</v>
       </c>
@@ -3956,7 +3958,7 @@
       <c r="BA16" s="9"/>
       <c r="BB16" s="10"/>
     </row>
-    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:54">
       <c r="A17" s="5">
         <v>9</v>
       </c>
@@ -4014,7 +4016,7 @@
       <c r="BA17" s="9"/>
       <c r="BB17" s="10"/>
     </row>
-    <row r="18" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:54">
       <c r="A18" s="12">
         <v>10</v>
       </c>
@@ -4072,7 +4074,7 @@
       <c r="BA18" s="16"/>
       <c r="BB18" s="17"/>
     </row>
-    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:54">
       <c r="A19" s="5" t="s">
         <v>44</v>
       </c>
@@ -4081,56 +4083,56 @@
       <c r="D19" s="18"/>
       <c r="E19" s="18"/>
       <c r="F19" s="7"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="30"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="25"/>
-      <c r="N19" s="26"/>
-      <c r="O19" s="30"/>
-      <c r="P19" s="25"/>
-      <c r="Q19" s="25"/>
-      <c r="R19" s="26"/>
-      <c r="S19" s="30"/>
-      <c r="T19" s="25"/>
-      <c r="U19" s="25"/>
-      <c r="V19" s="26"/>
-      <c r="W19" s="30"/>
-      <c r="X19" s="25"/>
-      <c r="Y19" s="25"/>
-      <c r="Z19" s="26"/>
-      <c r="AA19" s="30"/>
-      <c r="AB19" s="25"/>
-      <c r="AC19" s="25"/>
-      <c r="AD19" s="26"/>
-      <c r="AE19" s="30"/>
-      <c r="AF19" s="25"/>
-      <c r="AG19" s="25"/>
-      <c r="AH19" s="26"/>
-      <c r="AI19" s="30"/>
-      <c r="AJ19" s="25"/>
-      <c r="AK19" s="25"/>
-      <c r="AL19" s="26"/>
-      <c r="AM19" s="30"/>
-      <c r="AN19" s="25"/>
-      <c r="AO19" s="25"/>
-      <c r="AP19" s="26"/>
-      <c r="AQ19" s="30"/>
-      <c r="AR19" s="25"/>
-      <c r="AS19" s="25"/>
-      <c r="AT19" s="26"/>
-      <c r="AU19" s="30"/>
-      <c r="AV19" s="25"/>
-      <c r="AW19" s="25"/>
-      <c r="AX19" s="26"/>
-      <c r="AY19" s="30"/>
-      <c r="AZ19" s="25"/>
-      <c r="BA19" s="25"/>
-      <c r="BB19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="27"/>
+      <c r="Q19" s="27"/>
+      <c r="R19" s="28"/>
+      <c r="S19" s="26"/>
+      <c r="T19" s="27"/>
+      <c r="U19" s="27"/>
+      <c r="V19" s="28"/>
+      <c r="W19" s="26"/>
+      <c r="X19" s="27"/>
+      <c r="Y19" s="27"/>
+      <c r="Z19" s="28"/>
+      <c r="AA19" s="26"/>
+      <c r="AB19" s="27"/>
+      <c r="AC19" s="27"/>
+      <c r="AD19" s="28"/>
+      <c r="AE19" s="26"/>
+      <c r="AF19" s="27"/>
+      <c r="AG19" s="27"/>
+      <c r="AH19" s="28"/>
+      <c r="AI19" s="26"/>
+      <c r="AJ19" s="27"/>
+      <c r="AK19" s="27"/>
+      <c r="AL19" s="28"/>
+      <c r="AM19" s="26"/>
+      <c r="AN19" s="27"/>
+      <c r="AO19" s="27"/>
+      <c r="AP19" s="28"/>
+      <c r="AQ19" s="26"/>
+      <c r="AR19" s="27"/>
+      <c r="AS19" s="27"/>
+      <c r="AT19" s="28"/>
+      <c r="AU19" s="26"/>
+      <c r="AV19" s="27"/>
+      <c r="AW19" s="27"/>
+      <c r="AX19" s="28"/>
+      <c r="AY19" s="26"/>
+      <c r="AZ19" s="27"/>
+      <c r="BA19" s="27"/>
+      <c r="BB19" s="28"/>
     </row>
-    <row r="20" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:54" ht="15.95" thickBot="1">
       <c r="A20" s="5" t="s">
         <v>45</v>
       </c>
@@ -4139,56 +4141,56 @@
       <c r="D20" s="18"/>
       <c r="E20" s="18"/>
       <c r="F20" s="7"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="27"/>
-      <c r="M20" s="27"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="29"/>
-      <c r="P20" s="27"/>
-      <c r="Q20" s="27"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="27"/>
-      <c r="U20" s="27"/>
-      <c r="V20" s="28"/>
-      <c r="W20" s="29"/>
-      <c r="X20" s="27"/>
-      <c r="Y20" s="27"/>
-      <c r="Z20" s="28"/>
-      <c r="AA20" s="29"/>
-      <c r="AB20" s="27"/>
-      <c r="AC20" s="27"/>
-      <c r="AD20" s="28"/>
-      <c r="AE20" s="29"/>
-      <c r="AF20" s="27"/>
-      <c r="AG20" s="27"/>
-      <c r="AH20" s="28"/>
-      <c r="AI20" s="29"/>
-      <c r="AJ20" s="27"/>
-      <c r="AK20" s="27"/>
-      <c r="AL20" s="28"/>
-      <c r="AM20" s="29"/>
-      <c r="AN20" s="27"/>
-      <c r="AO20" s="27"/>
-      <c r="AP20" s="28"/>
-      <c r="AQ20" s="29"/>
-      <c r="AR20" s="27"/>
-      <c r="AS20" s="27"/>
-      <c r="AT20" s="28"/>
-      <c r="AU20" s="29"/>
-      <c r="AV20" s="27"/>
-      <c r="AW20" s="27"/>
-      <c r="AX20" s="28"/>
-      <c r="AY20" s="29"/>
-      <c r="AZ20" s="27"/>
-      <c r="BA20" s="27"/>
-      <c r="BB20" s="28"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="23"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="23"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="24"/>
+      <c r="R20" s="25"/>
+      <c r="S20" s="23"/>
+      <c r="T20" s="24"/>
+      <c r="U20" s="24"/>
+      <c r="V20" s="25"/>
+      <c r="W20" s="23"/>
+      <c r="X20" s="24"/>
+      <c r="Y20" s="24"/>
+      <c r="Z20" s="25"/>
+      <c r="AA20" s="23"/>
+      <c r="AB20" s="24"/>
+      <c r="AC20" s="24"/>
+      <c r="AD20" s="25"/>
+      <c r="AE20" s="23"/>
+      <c r="AF20" s="24"/>
+      <c r="AG20" s="24"/>
+      <c r="AH20" s="25"/>
+      <c r="AI20" s="23"/>
+      <c r="AJ20" s="24"/>
+      <c r="AK20" s="24"/>
+      <c r="AL20" s="25"/>
+      <c r="AM20" s="23"/>
+      <c r="AN20" s="24"/>
+      <c r="AO20" s="24"/>
+      <c r="AP20" s="25"/>
+      <c r="AQ20" s="23"/>
+      <c r="AR20" s="24"/>
+      <c r="AS20" s="24"/>
+      <c r="AT20" s="25"/>
+      <c r="AU20" s="23"/>
+      <c r="AV20" s="24"/>
+      <c r="AW20" s="24"/>
+      <c r="AX20" s="25"/>
+      <c r="AY20" s="23"/>
+      <c r="AZ20" s="24"/>
+      <c r="BA20" s="24"/>
+      <c r="BB20" s="25"/>
     </row>
-    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:54">
       <c r="A21" s="5" t="s">
         <v>46</v>
       </c>
@@ -4197,56 +4199,56 @@
       <c r="D21" s="19"/>
       <c r="E21" s="19"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
-      <c r="S21" s="23"/>
-      <c r="T21" s="23"/>
-      <c r="U21" s="23"/>
-      <c r="V21" s="23"/>
-      <c r="W21" s="23"/>
-      <c r="X21" s="23"/>
-      <c r="Y21" s="23"/>
-      <c r="Z21" s="23"/>
-      <c r="AA21" s="23"/>
-      <c r="AB21" s="23"/>
-      <c r="AC21" s="23"/>
-      <c r="AD21" s="23"/>
-      <c r="AE21" s="23"/>
-      <c r="AF21" s="23"/>
-      <c r="AG21" s="23"/>
-      <c r="AH21" s="23"/>
-      <c r="AI21" s="23"/>
-      <c r="AJ21" s="23"/>
-      <c r="AK21" s="23"/>
-      <c r="AL21" s="23"/>
-      <c r="AM21" s="23"/>
-      <c r="AN21" s="23"/>
-      <c r="AO21" s="23"/>
-      <c r="AP21" s="23"/>
-      <c r="AQ21" s="23"/>
-      <c r="AR21" s="23"/>
-      <c r="AS21" s="23"/>
-      <c r="AT21" s="23"/>
-      <c r="AU21" s="23"/>
-      <c r="AV21" s="23"/>
-      <c r="AW21" s="23"/>
-      <c r="AX21" s="23"/>
-      <c r="AY21" s="23"/>
-      <c r="AZ21" s="23"/>
-      <c r="BA21" s="23"/>
-      <c r="BB21" s="24"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32"/>
+      <c r="N21" s="32"/>
+      <c r="O21" s="32"/>
+      <c r="P21" s="32"/>
+      <c r="Q21" s="32"/>
+      <c r="R21" s="32"/>
+      <c r="S21" s="32"/>
+      <c r="T21" s="32"/>
+      <c r="U21" s="32"/>
+      <c r="V21" s="32"/>
+      <c r="W21" s="32"/>
+      <c r="X21" s="32"/>
+      <c r="Y21" s="32"/>
+      <c r="Z21" s="32"/>
+      <c r="AA21" s="32"/>
+      <c r="AB21" s="32"/>
+      <c r="AC21" s="32"/>
+      <c r="AD21" s="32"/>
+      <c r="AE21" s="32"/>
+      <c r="AF21" s="32"/>
+      <c r="AG21" s="32"/>
+      <c r="AH21" s="32"/>
+      <c r="AI21" s="32"/>
+      <c r="AJ21" s="32"/>
+      <c r="AK21" s="32"/>
+      <c r="AL21" s="32"/>
+      <c r="AM21" s="32"/>
+      <c r="AN21" s="32"/>
+      <c r="AO21" s="32"/>
+      <c r="AP21" s="32"/>
+      <c r="AQ21" s="32"/>
+      <c r="AR21" s="32"/>
+      <c r="AS21" s="32"/>
+      <c r="AT21" s="32"/>
+      <c r="AU21" s="32"/>
+      <c r="AV21" s="32"/>
+      <c r="AW21" s="32"/>
+      <c r="AX21" s="32"/>
+      <c r="AY21" s="32"/>
+      <c r="AZ21" s="32"/>
+      <c r="BA21" s="32"/>
+      <c r="BB21" s="33"/>
     </row>
-    <row r="22" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:54">
       <c r="A22" s="5" t="s">
         <v>47</v>
       </c>
@@ -4255,56 +4257,56 @@
       <c r="D22" s="19"/>
       <c r="E22" s="19"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="25"/>
-      <c r="L22" s="25"/>
-      <c r="M22" s="25"/>
-      <c r="N22" s="25"/>
-      <c r="O22" s="25"/>
-      <c r="P22" s="25"/>
-      <c r="Q22" s="25"/>
-      <c r="R22" s="25"/>
-      <c r="S22" s="25"/>
-      <c r="T22" s="25"/>
-      <c r="U22" s="25"/>
-      <c r="V22" s="25"/>
-      <c r="W22" s="25"/>
-      <c r="X22" s="25"/>
-      <c r="Y22" s="25"/>
-      <c r="Z22" s="25"/>
-      <c r="AA22" s="25"/>
-      <c r="AB22" s="25"/>
-      <c r="AC22" s="25"/>
-      <c r="AD22" s="25"/>
-      <c r="AE22" s="25"/>
-      <c r="AF22" s="25"/>
-      <c r="AG22" s="25"/>
-      <c r="AH22" s="25"/>
-      <c r="AI22" s="25"/>
-      <c r="AJ22" s="25"/>
-      <c r="AK22" s="25"/>
-      <c r="AL22" s="25"/>
-      <c r="AM22" s="25"/>
-      <c r="AN22" s="25"/>
-      <c r="AO22" s="25"/>
-      <c r="AP22" s="25"/>
-      <c r="AQ22" s="25"/>
-      <c r="AR22" s="25"/>
-      <c r="AS22" s="25"/>
-      <c r="AT22" s="25"/>
-      <c r="AU22" s="25"/>
-      <c r="AV22" s="25"/>
-      <c r="AW22" s="25"/>
-      <c r="AX22" s="25"/>
-      <c r="AY22" s="25"/>
-      <c r="AZ22" s="25"/>
-      <c r="BA22" s="25"/>
-      <c r="BB22" s="26"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="27"/>
+      <c r="K22" s="27"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="27"/>
+      <c r="N22" s="27"/>
+      <c r="O22" s="27"/>
+      <c r="P22" s="27"/>
+      <c r="Q22" s="27"/>
+      <c r="R22" s="27"/>
+      <c r="S22" s="27"/>
+      <c r="T22" s="27"/>
+      <c r="U22" s="27"/>
+      <c r="V22" s="27"/>
+      <c r="W22" s="27"/>
+      <c r="X22" s="27"/>
+      <c r="Y22" s="27"/>
+      <c r="Z22" s="27"/>
+      <c r="AA22" s="27"/>
+      <c r="AB22" s="27"/>
+      <c r="AC22" s="27"/>
+      <c r="AD22" s="27"/>
+      <c r="AE22" s="27"/>
+      <c r="AF22" s="27"/>
+      <c r="AG22" s="27"/>
+      <c r="AH22" s="27"/>
+      <c r="AI22" s="27"/>
+      <c r="AJ22" s="27"/>
+      <c r="AK22" s="27"/>
+      <c r="AL22" s="27"/>
+      <c r="AM22" s="27"/>
+      <c r="AN22" s="27"/>
+      <c r="AO22" s="27"/>
+      <c r="AP22" s="27"/>
+      <c r="AQ22" s="27"/>
+      <c r="AR22" s="27"/>
+      <c r="AS22" s="27"/>
+      <c r="AT22" s="27"/>
+      <c r="AU22" s="27"/>
+      <c r="AV22" s="27"/>
+      <c r="AW22" s="27"/>
+      <c r="AX22" s="27"/>
+      <c r="AY22" s="27"/>
+      <c r="AZ22" s="27"/>
+      <c r="BA22" s="27"/>
+      <c r="BB22" s="28"/>
     </row>
-    <row r="23" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:54" ht="15.95" thickBot="1">
       <c r="A23" s="20" t="s">
         <v>48</v>
       </c>
@@ -4313,94 +4315,70 @@
       <c r="D23" s="21"/>
       <c r="E23" s="21"/>
       <c r="F23" s="22"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="P23" s="27"/>
-      <c r="Q23" s="27"/>
-      <c r="R23" s="27"/>
-      <c r="S23" s="27"/>
-      <c r="T23" s="27"/>
-      <c r="U23" s="27"/>
-      <c r="V23" s="27"/>
-      <c r="W23" s="27"/>
-      <c r="X23" s="27"/>
-      <c r="Y23" s="27"/>
-      <c r="Z23" s="27"/>
-      <c r="AA23" s="27"/>
-      <c r="AB23" s="27"/>
-      <c r="AC23" s="27"/>
-      <c r="AD23" s="27"/>
-      <c r="AE23" s="27"/>
-      <c r="AF23" s="27"/>
-      <c r="AG23" s="27"/>
-      <c r="AH23" s="27"/>
-      <c r="AI23" s="27"/>
-      <c r="AJ23" s="27"/>
-      <c r="AK23" s="27"/>
-      <c r="AL23" s="27"/>
-      <c r="AM23" s="27"/>
-      <c r="AN23" s="27"/>
-      <c r="AO23" s="27"/>
-      <c r="AP23" s="27"/>
-      <c r="AQ23" s="27"/>
-      <c r="AR23" s="27"/>
-      <c r="AS23" s="27"/>
-      <c r="AT23" s="27"/>
-      <c r="AU23" s="27"/>
-      <c r="AV23" s="27"/>
-      <c r="AW23" s="27"/>
-      <c r="AX23" s="27"/>
-      <c r="AY23" s="27"/>
-      <c r="AZ23" s="27"/>
-      <c r="BA23" s="27"/>
-      <c r="BB23" s="28"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
+      <c r="N23" s="24"/>
+      <c r="O23" s="24"/>
+      <c r="P23" s="24"/>
+      <c r="Q23" s="24"/>
+      <c r="R23" s="24"/>
+      <c r="S23" s="24"/>
+      <c r="T23" s="24"/>
+      <c r="U23" s="24"/>
+      <c r="V23" s="24"/>
+      <c r="W23" s="24"/>
+      <c r="X23" s="24"/>
+      <c r="Y23" s="24"/>
+      <c r="Z23" s="24"/>
+      <c r="AA23" s="24"/>
+      <c r="AB23" s="24"/>
+      <c r="AC23" s="24"/>
+      <c r="AD23" s="24"/>
+      <c r="AE23" s="24"/>
+      <c r="AF23" s="24"/>
+      <c r="AG23" s="24"/>
+      <c r="AH23" s="24"/>
+      <c r="AI23" s="24"/>
+      <c r="AJ23" s="24"/>
+      <c r="AK23" s="24"/>
+      <c r="AL23" s="24"/>
+      <c r="AM23" s="24"/>
+      <c r="AN23" s="24"/>
+      <c r="AO23" s="24"/>
+      <c r="AP23" s="24"/>
+      <c r="AQ23" s="24"/>
+      <c r="AR23" s="24"/>
+      <c r="AS23" s="24"/>
+      <c r="AT23" s="24"/>
+      <c r="AU23" s="24"/>
+      <c r="AV23" s="24"/>
+      <c r="AW23" s="24"/>
+      <c r="AX23" s="24"/>
+      <c r="AY23" s="24"/>
+      <c r="AZ23" s="24"/>
+      <c r="BA23" s="24"/>
+      <c r="BB23" s="25"/>
     </row>
-    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:54">
       <c r="A24" s="1" t="s">
         <v>49</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="G23:AD23"/>
-    <mergeCell ref="AE23:BB23"/>
-    <mergeCell ref="AU20:AX20"/>
-    <mergeCell ref="AY20:BB20"/>
-    <mergeCell ref="G21:AD21"/>
-    <mergeCell ref="AE21:BB21"/>
-    <mergeCell ref="G22:AD22"/>
-    <mergeCell ref="AE22:BB22"/>
-    <mergeCell ref="AA20:AD20"/>
-    <mergeCell ref="AE20:AH20"/>
-    <mergeCell ref="AI20:AL20"/>
-    <mergeCell ref="AM20:AP20"/>
-    <mergeCell ref="AQ20:AT20"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="K20:N20"/>
-    <mergeCell ref="O20:R20"/>
-    <mergeCell ref="S20:V20"/>
-    <mergeCell ref="W20:Z20"/>
-    <mergeCell ref="AY7:BB7"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="K19:N19"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="S19:V19"/>
-    <mergeCell ref="W19:Z19"/>
-    <mergeCell ref="AA19:AD19"/>
-    <mergeCell ref="AE19:AH19"/>
-    <mergeCell ref="AI19:AL19"/>
-    <mergeCell ref="AM19:AP19"/>
-    <mergeCell ref="AQ19:AT19"/>
-    <mergeCell ref="AU19:AX19"/>
-    <mergeCell ref="AY19:BB19"/>
-    <mergeCell ref="AE7:AH7"/>
+    <mergeCell ref="S7:V7"/>
+    <mergeCell ref="W7:Z7"/>
+    <mergeCell ref="AA7:AD7"/>
+    <mergeCell ref="A1:BB1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="G2:BB2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="G3:BB3"/>
     <mergeCell ref="AI7:AL7"/>
     <mergeCell ref="AM7:AP7"/>
     <mergeCell ref="AQ7:AT7"/>
@@ -4417,17 +4395,308 @@
     <mergeCell ref="G6:BB6"/>
     <mergeCell ref="G7:J7"/>
     <mergeCell ref="K7:N7"/>
+    <mergeCell ref="S20:V20"/>
+    <mergeCell ref="W20:Z20"/>
+    <mergeCell ref="AY7:BB7"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="K19:N19"/>
+    <mergeCell ref="O19:R19"/>
+    <mergeCell ref="S19:V19"/>
+    <mergeCell ref="W19:Z19"/>
+    <mergeCell ref="AA19:AD19"/>
+    <mergeCell ref="AE19:AH19"/>
+    <mergeCell ref="AI19:AL19"/>
+    <mergeCell ref="AM19:AP19"/>
+    <mergeCell ref="AU19:AX19"/>
+    <mergeCell ref="AY19:BB19"/>
+    <mergeCell ref="AE7:AH7"/>
+    <mergeCell ref="G23:AD23"/>
+    <mergeCell ref="AE23:BB23"/>
+    <mergeCell ref="AU20:AX20"/>
+    <mergeCell ref="AY20:BB20"/>
+    <mergeCell ref="G21:AD21"/>
+    <mergeCell ref="AE21:BB21"/>
+    <mergeCell ref="G22:AD22"/>
+    <mergeCell ref="AE22:BB22"/>
+    <mergeCell ref="AA20:AD20"/>
+    <mergeCell ref="AE20:AH20"/>
+    <mergeCell ref="AI20:AL20"/>
+    <mergeCell ref="AM20:AP20"/>
     <mergeCell ref="O7:R7"/>
-    <mergeCell ref="S7:V7"/>
-    <mergeCell ref="W7:Z7"/>
-    <mergeCell ref="AA7:AD7"/>
-    <mergeCell ref="A1:BB1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:BB2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="G3:BB3"/>
+    <mergeCell ref="AQ20:AT20"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="K20:N20"/>
+    <mergeCell ref="O20:R20"/>
+    <mergeCell ref="AQ19:AT19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="13c90a0b-73bc-4dc0-be5f-28d77b615beb" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="13c93bba-48ce-428c-bfe5-88b42c19b028">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101006A81D6BD42E8DF4C91013959704817E1" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="bf4f72ffd194f0963ff564daca6869f7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="13c90a0b-73bc-4dc0-be5f-28d77b615beb" xmlns:ns3="13c93bba-48ce-428c-bfe5-88b42c19b028" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8718d6f4873a5b1392a45044efa78385" ns2:_="" ns3:_="">
+    <xsd:import namespace="13c90a0b-73bc-4dc0-be5f-28d77b615beb"/>
+    <xsd:import namespace="13c93bba-48ce-428c-bfe5-88b42c19b028"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="13c90a0b-73bc-4dc0-be5f-28d77b615beb" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{a42ca037-5d13-4729-aeec-4237f141d2d6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="13c90a0b-73bc-4dc0-be5f-28d77b615beb">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="13c93bba-48ce-428c-bfe5-88b42c19b028" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="12" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="13" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="d33c8c81-5745-4931-bcc4-c2aeafe86780" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3BD9A89-9A37-4DE5-B60C-51B89122CDBB}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50E51DBE-5FA0-4121-870F-585FBCC43CF6}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2790E436-9388-4181-B5D6-275AEB65AD94}"/>
 </file>